--- a/multi seed generators/second batch/classification/results/aggregated/fidelity_mean_sd.xlsx
+++ b/multi seed generators/second batch/classification/results/aggregated/fidelity_mean_sd.xlsx
@@ -999,12 +999,10 @@
       <c r="H18" s="2" t="n">
         <v>0.7079166666666666</v>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I18" s="2"/>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.707917 ± 0</t>
+          <t xml:space="preserve">0.707917</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -1049,12 +1047,10 @@
       <c r="H19" t="n">
         <v>0.3760959102831625</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I19"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.376096 ± 0</t>
+          <t xml:space="preserve">0.376096</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1099,12 +1095,10 @@
       <c r="H20" s="2" t="n">
         <v>0.7883588541666665</v>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I20" s="2"/>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.788359 ± 0</t>
+          <t xml:space="preserve">0.788359</t>
         </is>
       </c>
       <c r="K20" s="2" t="n">
@@ -1149,12 +1143,10 @@
       <c r="H21" t="n">
         <v>2115.559874999999</v>
       </c>
-      <c r="I21" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I21"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115.56 ± 0</t>
+          <t xml:space="preserve">2115.56</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2599,12 +2591,10 @@
       <c r="H50" s="2" t="n">
         <v>0.8702384450566268</v>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I50" s="2"/>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.870238 ± 0</t>
+          <t xml:space="preserve">0.870238</t>
         </is>
       </c>
       <c r="K50" s="2" t="n">
@@ -2649,12 +2639,10 @@
       <c r="H51" t="n">
         <v>0.05358624166990889</v>
       </c>
-      <c r="I51" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I51"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0535862 ± 0</t>
+          <t xml:space="preserve">0.0535862</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -2699,12 +2687,10 @@
       <c r="H52" s="2" t="n">
         <v>0.7942522552061084</v>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I52" s="2"/>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.794252 ± 0</t>
+          <t xml:space="preserve">0.794252</t>
         </is>
       </c>
       <c r="K52" s="2" t="n">
@@ -2749,12 +2735,10 @@
       <c r="H53" t="n">
         <v>42.22296198136731</v>
       </c>
-      <c r="I53" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I53"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">42.223 ± 0</t>
+          <t xml:space="preserve">42.223</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -4199,12 +4183,10 @@
       <c r="H82" s="2" t="n">
         <v>0.8728571428571429</v>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I82" s="2"/>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.872857 ± 0</t>
+          <t xml:space="preserve">0.872857</t>
         </is>
       </c>
       <c r="K82" s="2" t="n">
@@ -4249,12 +4231,10 @@
       <c r="H83" t="n">
         <v>0.009848353633469697</v>
       </c>
-      <c r="I83" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I83"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.00984835 ± 0</t>
+          <t xml:space="preserve">0.00984835</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -4299,12 +4279,10 @@
       <c r="H84" s="2" t="n">
         <v>0.8551804329462943</v>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I84" s="2"/>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.85518 ± 0</t>
+          <t xml:space="preserve">0.85518</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
@@ -4349,12 +4327,10 @@
       <c r="H85" t="n">
         <v>90.60117857142855</v>
       </c>
-      <c r="I85" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I85"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">90.6012 ± 0</t>
+          <t xml:space="preserve">90.6012</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -5099,12 +5075,10 @@
       <c r="H100" s="2" t="n">
         <v>3.4027777550415263e-10</v>
       </c>
-      <c r="I100" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I100" s="2"/>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.40278e-10 ± 0</t>
+          <t xml:space="preserve">3.40278e-10</t>
         </is>
       </c>
       <c r="K100" s="2" t="n">
@@ -5799,12 +5773,10 @@
       <c r="H114" s="2" t="n">
         <v>0.9530795454545457</v>
       </c>
-      <c r="I114" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I114" s="2"/>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.95308 ± 0</t>
+          <t xml:space="preserve">0.95308</t>
         </is>
       </c>
       <c r="K114" s="2" t="n">
@@ -5849,12 +5821,10 @@
       <c r="H115" t="n">
         <v>0.06812873655465546</v>
       </c>
-      <c r="I115" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I115"/>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0681287 ± 0</t>
+          <t xml:space="preserve">0.0681287</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -5899,12 +5869,10 @@
       <c r="H116" s="2" t="n">
         <v>0.9111395202020202</v>
       </c>
-      <c r="I116" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I116" s="2"/>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.91114 ± 0</t>
+          <t xml:space="preserve">0.91114</t>
         </is>
       </c>
       <c r="K116" s="2" t="n">
@@ -5949,12 +5917,10 @@
       <c r="H117" t="n">
         <v>0.7336818181818184</v>
       </c>
-      <c r="I117" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I117"/>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.733682 ± 0</t>
+          <t xml:space="preserve">0.733682</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -7399,12 +7365,10 @@
       <c r="H146" s="2" t="n">
         <v>0.9201659340659342</v>
       </c>
-      <c r="I146" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I146" s="2"/>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.920166 ± 0</t>
+          <t xml:space="preserve">0.920166</t>
         </is>
       </c>
       <c r="K146" s="2" t="n">
@@ -7449,12 +7413,10 @@
       <c r="H147" t="n">
         <v>0.01731580577291802</v>
       </c>
-      <c r="I147" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I147"/>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0173158 ± 0</t>
+          <t xml:space="preserve">0.0173158</t>
         </is>
       </c>
       <c r="K147" t="n">
@@ -7499,12 +7461,10 @@
       <c r="H148" s="2" t="n">
         <v>0.9311545522289846</v>
       </c>
-      <c r="I148" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I148" s="2"/>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.931155 ± 0</t>
+          <t xml:space="preserve">0.931155</t>
         </is>
       </c>
       <c r="K148" s="2" t="n">
@@ -7549,12 +7509,10 @@
       <c r="H149" t="n">
         <v>3.709512133153039</v>
       </c>
-      <c r="I149" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I149"/>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.70951 ± 0</t>
+          <t xml:space="preserve">3.70951</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -8999,12 +8957,10 @@
       <c r="H178" s="2" t="n">
         <v>0.9765954545454543</v>
       </c>
-      <c r="I178" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I178" s="2"/>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.976595 ± 0</t>
+          <t xml:space="preserve">0.976595</t>
         </is>
       </c>
       <c r="K178" s="2" t="n">
@@ -9049,12 +9005,10 @@
       <c r="H179" t="n">
         <v>0.02178163914459408</v>
       </c>
-      <c r="I179" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I179"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0217816 ± 0</t>
+          <t xml:space="preserve">0.0217816</t>
         </is>
       </c>
       <c r="K179" t="n">
@@ -9099,12 +9053,10 @@
       <c r="H180" s="2" t="n">
         <v>0.9220989336183831</v>
       </c>
-      <c r="I180" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I180" s="2"/>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.922099 ± 0</t>
+          <t xml:space="preserve">0.922099</t>
         </is>
       </c>
       <c r="K180" s="2" t="n">
@@ -9149,12 +9101,10 @@
       <c r="H181" t="n">
         <v>6.416240909090907</v>
       </c>
-      <c r="I181" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I181"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.41624 ± 0</t>
+          <t xml:space="preserve">6.41624</t>
         </is>
       </c>
       <c r="K181" t="n">
@@ -9649,12 +9599,10 @@
       <c r="H191" t="n">
         <v>0.334484855433916</v>
       </c>
-      <c r="I191" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I191"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.334485 ± 0</t>
+          <t xml:space="preserve">0.334485</t>
         </is>
       </c>
       <c r="K191" t="n">
@@ -10599,12 +10547,10 @@
       <c r="H210" s="2" t="n">
         <v>0.9134500000000001</v>
       </c>
-      <c r="I210" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I210" s="2"/>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.91345 ± 0</t>
+          <t xml:space="preserve">0.91345</t>
         </is>
       </c>
       <c r="K210" s="2" t="n">
@@ -10649,12 +10595,10 @@
       <c r="H211" t="n">
         <v>0.02798671692079346</v>
       </c>
-      <c r="I211" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I211"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0279867 ± 0</t>
+          <t xml:space="preserve">0.0279867</t>
         </is>
       </c>
       <c r="K211" t="n">
@@ -10699,12 +10643,10 @@
       <c r="H212" s="2" t="n">
         <v>0.8893182921814837</v>
       </c>
-      <c r="I212" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I212" s="2"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.889318 ± 0</t>
+          <t xml:space="preserve">0.889318</t>
         </is>
       </c>
       <c r="K212" s="2" t="n">
@@ -10749,12 +10691,10 @@
       <c r="H213" t="n">
         <v>5.203521939999999</v>
       </c>
-      <c r="I213" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I213"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.20352 ± 0</t>
+          <t xml:space="preserve">5.20352</t>
         </is>
       </c>
       <c r="K213" t="n">
@@ -12199,12 +12139,10 @@
       <c r="H242" s="2" t="n">
         <v>0.9239166666666666</v>
       </c>
-      <c r="I242" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I242" s="2"/>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.923917 ± 0</t>
+          <t xml:space="preserve">0.923917</t>
         </is>
       </c>
       <c r="K242" s="2" t="n">
@@ -12249,12 +12187,10 @@
       <c r="H243" t="n">
         <v>0.009532587279207694</v>
       </c>
-      <c r="I243" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I243"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.00953259 ± 0</t>
+          <t xml:space="preserve">0.00953259</t>
         </is>
       </c>
       <c r="K243" t="n">
@@ -12299,12 +12235,10 @@
       <c r="H244" s="2" t="n">
         <v>0.8985806959757218</v>
       </c>
-      <c r="I244" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I244" s="2"/>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.898581 ± 0</t>
+          <t xml:space="preserve">0.898581</t>
         </is>
       </c>
       <c r="K244" s="2" t="n">
@@ -12349,12 +12283,10 @@
       <c r="H245" t="n">
         <v>0.7030033333333329</v>
       </c>
-      <c r="I245" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I245"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.703003 ± 0</t>
+          <t xml:space="preserve">0.703003</t>
         </is>
       </c>
       <c r="K245" t="n">
@@ -13799,12 +13731,10 @@
       <c r="H274" s="2" t="n">
         <v>0.8933956950825249</v>
       </c>
-      <c r="I274" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I274" s="2"/>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.893396 ± 0</t>
+          <t xml:space="preserve">0.893396</t>
         </is>
       </c>
       <c r="K274" s="2" t="n">
@@ -13849,12 +13779,10 @@
       <c r="H275" t="n">
         <v>0.0742191093104625</v>
       </c>
-      <c r="I275" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I275"/>
       <c r="J275" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.0742191 ± 0</t>
+          <t xml:space="preserve">0.0742191</t>
         </is>
       </c>
       <c r="K275" t="n">
@@ -13899,12 +13827,10 @@
       <c r="H276" s="2" t="n">
         <v>0.9382852305742174</v>
       </c>
-      <c r="I276" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I276" s="2"/>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.938285 ± 0</t>
+          <t xml:space="preserve">0.938285</t>
         </is>
       </c>
       <c r="K276" s="2" t="n">
@@ -13949,12 +13875,10 @@
       <c r="H277" t="n">
         <v>0.339739220973996</v>
       </c>
-      <c r="I277" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I277"/>
       <c r="J277" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.339739 ± 0</t>
+          <t xml:space="preserve">0.339739</t>
         </is>
       </c>
       <c r="K277" t="n">
